--- a/grupos/5AEM - Estadisticos 20211.xlsx
+++ b/grupos/5AEM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="160">
   <si>
     <t>Materia</t>
   </si>
@@ -200,24 +200,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
+    <t>Cruz Alejo José Armando</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Cruz Alejo José Armando</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
     <t>Aurioles Maldonado Luis Gustavo</t>
   </si>
   <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -230,274 +230,274 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VALDERRAMA</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MENCIAS</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>FERNANDO DE JESUS</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>ESTEFANY SARAI</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>NATANAEL</t>
+  </si>
+  <si>
+    <t>YAMIL ELIEL</t>
+  </si>
+  <si>
+    <t>ERICK ORLANDO</t>
+  </si>
+  <si>
+    <t>EMILIO</t>
+  </si>
+  <si>
+    <t>ALAN EDUARDO</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BALDEZ</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>MORALES</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
   </si>
   <si>
     <t>TEPOLE</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>VALENCIA</t>
   </si>
   <si>
-    <t>VALDERRAMA</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
     <t>MORAN</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>IXTACUA</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>PALAGOT</t>
+  </si>
+  <si>
+    <t>BELTRAN</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>YEPEZ</t>
   </si>
   <si>
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MENCIAS</t>
+    <t>MELLADO</t>
   </si>
   <si>
     <t>JOSE MANUEL</t>
   </si>
   <si>
-    <t>FERNANDO DE JESUS</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>JESUS</t>
+    <t>CARLOS ALBERTO</t>
+  </si>
+  <si>
+    <t>ALEX SAUL</t>
+  </si>
+  <si>
+    <t>CRISTIAN ANTONIO</t>
+  </si>
+  <si>
+    <t>ALBERTO</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>HAZIEL</t>
+  </si>
+  <si>
+    <t>GIOVANNA</t>
+  </si>
+  <si>
+    <t>SAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>LOGAN ZURIEL</t>
   </si>
   <si>
     <t>YAIR ANTONIO</t>
   </si>
   <si>
-    <t>ESTEFANY SARAI</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>NATANAEL</t>
+    <t>HUGO</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>JOSE AUGUSTO</t>
+  </si>
+  <si>
+    <t>DIANA AMEYALLI</t>
+  </si>
+  <si>
+    <t>ANUAR ANTONIO</t>
   </si>
   <si>
     <t>ELIDETH</t>
   </si>
   <si>
-    <t>YAMIL ELIEL</t>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>ARLETH</t>
+  </si>
+  <si>
+    <t>JAHIR</t>
+  </si>
+  <si>
+    <t>JOCELYN BERENICE</t>
   </si>
   <si>
     <t>JOHNNY</t>
   </si>
   <si>
-    <t>ERICK ORLANDO</t>
-  </si>
-  <si>
     <t>MAURICIO</t>
-  </si>
-  <si>
-    <t>EMILIO</t>
-  </si>
-  <si>
-    <t>ALAN EDUARDO</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BALDEZ</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>IXTACUA</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>PALAGOT</t>
-  </si>
-  <si>
-    <t>BELTRAN</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>YEPEZ</t>
-  </si>
-  <si>
-    <t>MELLADO</t>
-  </si>
-  <si>
-    <t>CARLOS ALBERTO</t>
-  </si>
-  <si>
-    <t>ALEX SAUL</t>
-  </si>
-  <si>
-    <t>CRISTIAN ANTONIO</t>
-  </si>
-  <si>
-    <t>ALBERTO</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>HAZIEL</t>
-  </si>
-  <si>
-    <t>GIOVANNA</t>
-  </si>
-  <si>
-    <t>SAUL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>LOGAN ZURIEL</t>
-  </si>
-  <si>
-    <t>HUGO</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>JOSE AUGUSTO</t>
-  </si>
-  <si>
-    <t>DIANA AMEYALLI</t>
-  </si>
-  <si>
-    <t>ANUAR ANTONIO</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>ARLETH</t>
-  </si>
-  <si>
-    <t>JAHIR</t>
-  </si>
-  <si>
-    <t>JOCELYN BERENICE</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1002,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -1020,25 +1020,25 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1065,7 +1065,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -1109,25 +1109,25 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1151,10 +1151,10 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>8</v>
@@ -1198,25 +1198,25 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1287,25 +1287,25 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1355,46 +1355,46 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E8">
         <v>5</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G8">
         <v>-1</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1418,25 +1418,25 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z8">
         <v>5</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB8">
         <v>-1</v>
       </c>
       <c r="AC8">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1465,25 +1465,25 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1507,7 +1507,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>7</v>
@@ -1554,25 +1554,25 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1605,7 +1605,7 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA10">
         <v>10</v>
@@ -1643,25 +1643,25 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1685,16 +1685,16 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA11">
         <v>10</v>
@@ -1732,25 +1732,25 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1774,10 +1774,10 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>8</v>
@@ -1821,25 +1821,25 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1866,7 +1866,7 @@
         <v>10</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1892,7 +1892,7 @@
         <v>-1</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -1901,7 +1901,7 @@
         <v>6</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>7</v>
@@ -1913,22 +1913,22 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1955,16 +1955,16 @@
         <v>-1</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y14">
         <v>7</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB14">
         <v>7</v>
@@ -1981,43 +1981,43 @@
         <v>-1</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>5</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G15">
         <v>-1</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -2044,22 +2044,22 @@
         <v>-1</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z15">
         <v>5</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB15">
         <v>-1</v>
       </c>
       <c r="AC15">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2088,25 +2088,25 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2139,7 +2139,7 @@
         <v>9</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA16">
         <v>10</v>
@@ -2156,46 +2156,46 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>7</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E17">
         <v>5</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>-1</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2219,25 +2219,25 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB17">
         <v>-1</v>
       </c>
       <c r="AC17">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2266,25 +2266,25 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2314,10 +2314,10 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA18">
         <v>10</v>
@@ -2355,25 +2355,25 @@
         <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2406,7 +2406,7 @@
         <v>10</v>
       </c>
       <c r="Z19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA19">
         <v>10</v>
@@ -2426,7 +2426,7 @@
         <v>7</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -2444,25 +2444,25 @@
         <v>7</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2489,13 +2489,13 @@
         <v>7</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA20">
         <v>7</v>
@@ -2518,40 +2518,40 @@
         <v>6</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E21">
         <v>5</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G21">
         <v>-1</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I21">
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2578,22 +2578,22 @@
         <v>-1</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z21">
         <v>5</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB21">
         <v>-1</v>
       </c>
       <c r="AC21">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2622,25 +2622,25 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2667,13 +2667,13 @@
         <v>10</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -2693,10 +2693,10 @@
         <v>8</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E23">
         <v>7</v>
@@ -2711,25 +2711,25 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2753,16 +2753,16 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA23">
         <v>10</v>
@@ -2800,25 +2800,25 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2851,7 +2851,7 @@
         <v>8</v>
       </c>
       <c r="Z24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA24">
         <v>10</v>
@@ -2889,25 +2889,25 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2931,16 +2931,16 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y25">
         <v>8</v>
       </c>
       <c r="Z25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA25">
         <v>10</v>
@@ -2957,46 +2957,46 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C26">
         <v>6</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E26">
         <v>5</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G26">
         <v>7</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -3020,25 +3020,25 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z26">
         <v>5</v>
       </c>
       <c r="AA26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB26">
         <v>7</v>
       </c>
       <c r="AC26">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -3067,25 +3067,25 @@
         <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3115,10 +3115,10 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA27">
         <v>10</v>
@@ -3135,46 +3135,46 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E28">
         <v>5</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G28">
         <v>-1</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3198,25 +3198,25 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z28">
         <v>5</v>
       </c>
       <c r="AA28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB28">
         <v>-1</v>
       </c>
       <c r="AC28">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3245,25 +3245,25 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3290,13 +3290,13 @@
         <v>10</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>10</v>
       </c>
       <c r="Z29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA29">
         <v>10</v>
@@ -3334,25 +3334,25 @@
         <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3423,25 +3423,25 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3465,13 +3465,13 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z31">
         <v>7</v>
@@ -3512,25 +3512,25 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3557,13 +3557,13 @@
         <v>10</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y32">
         <v>10</v>
       </c>
       <c r="Z32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA32">
         <v>10</v>
@@ -3601,25 +3601,25 @@
         <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3646,7 +3646,7 @@
         <v>10</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y33">
         <v>9</v>
@@ -3669,13 +3669,13 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E34">
         <v>5</v>
@@ -3693,22 +3693,22 @@
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3732,13 +3732,13 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z34">
         <v>5</v>
@@ -3758,46 +3758,46 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E35">
         <v>8</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G35">
         <v>7</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3821,25 +3821,25 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB35">
         <v>7</v>
       </c>
       <c r="AC35">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3868,25 +3868,25 @@
         <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3913,13 +3913,13 @@
         <v>10</v>
       </c>
       <c r="X36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y36">
         <v>10</v>
       </c>
       <c r="Z36">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA36">
         <v>10</v>
@@ -3939,43 +3939,43 @@
         <v>-1</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E37">
         <v>5</v>
       </c>
       <c r="F37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G37">
         <v>-1</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I37">
         <v>-1</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N37">
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -4002,22 +4002,22 @@
         <v>-1</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z37">
         <v>5</v>
       </c>
       <c r="AA37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB37">
         <v>-1</v>
       </c>
       <c r="AC37">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -4025,7 +4025,7 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C38">
         <v>6</v>
@@ -4046,25 +4046,25 @@
         <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
         <v>-1</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -4088,16 +4088,16 @@
         <v>-1</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>6</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA38">
         <v>10</v>
@@ -4135,25 +4135,25 @@
         <v>10</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N39">
         <v>-1</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -4180,13 +4180,13 @@
         <v>10</v>
       </c>
       <c r="X39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y39">
         <v>9</v>
       </c>
       <c r="Z39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA39">
         <v>10</v>
@@ -4209,40 +4209,40 @@
         <v>6</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E40">
         <v>5</v>
       </c>
       <c r="F40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G40">
         <v>-1</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I40">
         <v>-1</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N40">
         <v>-1</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P40">
         <v>-1</v>
@@ -4272,19 +4272,19 @@
         <v>6</v>
       </c>
       <c r="Y40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z40">
         <v>5</v>
       </c>
       <c r="AA40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB40">
         <v>-1</v>
       </c>
       <c r="AC40">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -4292,46 +4292,46 @@
         <v>50</v>
       </c>
       <c r="B41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E41">
         <v>6</v>
       </c>
       <c r="F41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G41">
         <v>-1</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N41">
         <v>-1</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P41">
         <v>-1</v>
@@ -4355,25 +4355,25 @@
         <v>-1</v>
       </c>
       <c r="W41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB41">
         <v>-1</v>
       </c>
       <c r="AC41">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -4429,7 +4429,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
@@ -4438,13 +4438,13 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>65.79000000000001</v>
+        <v>68.42</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -4453,15 +4453,15 @@
         <v>9.1</v>
       </c>
       <c r="I2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J2">
-        <v>34.21</v>
+        <v>31.58</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -4470,30 +4470,30 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>73.68000000000001</v>
+      </c>
+      <c r="G3">
+        <v>26.32</v>
+      </c>
+      <c r="H3">
+        <v>7.1</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>68.42</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>9.1</v>
-      </c>
-      <c r="I3">
-        <v>12</v>
-      </c>
-      <c r="J3">
-        <v>31.58</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -4502,30 +4502,30 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E4">
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <v>78.95</v>
+      </c>
+      <c r="G4">
+        <v>21.05</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>68.42</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="I4">
-        <v>12</v>
-      </c>
-      <c r="J4">
-        <v>31.58</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -4534,30 +4534,30 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>81.58</v>
+      </c>
+      <c r="G5">
+        <v>18.42</v>
+      </c>
+      <c r="H5">
+        <v>7.7</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>71.05</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>7.3</v>
-      </c>
-      <c r="I5">
-        <v>11</v>
-      </c>
-      <c r="J5">
-        <v>28.95</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
@@ -4566,30 +4566,30 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>71.05</v>
+        <v>86.84</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>28.95</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
@@ -4598,19 +4598,19 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>73.68000000000001</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>26.32</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>9.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4624,31 +4624,31 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C8">
         <v>38</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>73.68000000000001</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4658,7 +4658,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4687,139 +4687,139 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920003</v>
+        <v>19330051920417</v>
       </c>
       <c r="B2" t="s">
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920417</v>
+        <v>19330051920014</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920417</v>
+        <v>19330051920014</v>
       </c>
       <c r="B4" t="s">
         <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920417</v>
+        <v>19330051920016</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920417</v>
+        <v>19330051920010</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920417</v>
+        <v>19330051920422</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920417</v>
+        <v>19330051920422</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>64</v>
@@ -4827,39 +4827,39 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920014</v>
+        <v>19330051920022</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920014</v>
+        <v>19330051920026</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>60</v>
@@ -4867,119 +4867,119 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920014</v>
+        <v>18330061460390</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
         <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920014</v>
+        <v>19330051920032</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
         <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920014</v>
+        <v>19330051920038</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920014</v>
+        <v>19330051920036</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920016</v>
+        <v>19330051920036</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920016</v>
+        <v>19330051920039</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
         <v>60</v>
@@ -4987,1082 +4987,42 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920016</v>
+        <v>19330051920039</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920016</v>
+        <v>19330051920040</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>19330051920016</v>
-      </c>
-      <c r="B19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" t="s">
-        <v>104</v>
-      </c>
-      <c r="E19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>19330051920010</v>
-      </c>
-      <c r="B20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" t="s">
-        <v>105</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>19330051920010</v>
-      </c>
-      <c r="B21" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21" t="s">
-        <v>105</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>19330051920010</v>
-      </c>
-      <c r="B22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" t="s">
-        <v>91</v>
-      </c>
-      <c r="D22" t="s">
-        <v>105</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>18330051920168</v>
-      </c>
-      <c r="B23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" t="s">
-        <v>106</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>19330051920422</v>
-      </c>
-      <c r="B24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" t="s">
-        <v>107</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19330051920422</v>
-      </c>
-      <c r="B25" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" t="s">
-        <v>92</v>
-      </c>
-      <c r="D25" t="s">
-        <v>107</v>
-      </c>
-      <c r="E25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330051920422</v>
-      </c>
-      <c r="B26" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" t="s">
-        <v>92</v>
-      </c>
-      <c r="D26" t="s">
-        <v>107</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19330051920422</v>
-      </c>
-      <c r="B27" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27" t="s">
-        <v>107</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>19330051920422</v>
-      </c>
-      <c r="B28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" t="s">
-        <v>92</v>
-      </c>
-      <c r="D28" t="s">
-        <v>107</v>
-      </c>
-      <c r="E28" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>19330051920022</v>
-      </c>
-      <c r="B29" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" t="s">
-        <v>93</v>
-      </c>
-      <c r="D29" t="s">
-        <v>108</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>19330051920022</v>
-      </c>
-      <c r="B30" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" t="s">
-        <v>93</v>
-      </c>
-      <c r="D30" t="s">
-        <v>108</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>19330051920022</v>
-      </c>
-      <c r="B31" t="s">
-        <v>76</v>
-      </c>
-      <c r="C31" t="s">
-        <v>93</v>
-      </c>
-      <c r="D31" t="s">
-        <v>108</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>19330051920026</v>
-      </c>
-      <c r="B32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" t="s">
-        <v>94</v>
-      </c>
-      <c r="D32" t="s">
-        <v>109</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>19330051920026</v>
-      </c>
-      <c r="B33" t="s">
-        <v>77</v>
-      </c>
-      <c r="C33" t="s">
-        <v>94</v>
-      </c>
-      <c r="D33" t="s">
-        <v>109</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>19330051920026</v>
-      </c>
-      <c r="B34" t="s">
-        <v>77</v>
-      </c>
-      <c r="C34" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34" t="s">
-        <v>109</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>19330051920026</v>
-      </c>
-      <c r="B35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35" t="s">
-        <v>94</v>
-      </c>
-      <c r="D35" t="s">
-        <v>109</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>19330051920026</v>
-      </c>
-      <c r="B36" t="s">
-        <v>77</v>
-      </c>
-      <c r="C36" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36" t="s">
-        <v>109</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>19330051920026</v>
-      </c>
-      <c r="B37" t="s">
-        <v>77</v>
-      </c>
-      <c r="C37" t="s">
-        <v>94</v>
-      </c>
-      <c r="D37" t="s">
-        <v>109</v>
-      </c>
-      <c r="E37" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>18330061460390</v>
-      </c>
-      <c r="B38" t="s">
-        <v>78</v>
-      </c>
-      <c r="C38" t="s">
-        <v>95</v>
-      </c>
-      <c r="D38" t="s">
-        <v>110</v>
-      </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>19330051920024</v>
-      </c>
-      <c r="B39" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" t="s">
-        <v>96</v>
-      </c>
-      <c r="D39" t="s">
-        <v>111</v>
-      </c>
-      <c r="E39" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>19330051920024</v>
-      </c>
-      <c r="B40" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" t="s">
-        <v>96</v>
-      </c>
-      <c r="D40" t="s">
-        <v>111</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>19330051920024</v>
-      </c>
-      <c r="B41" t="s">
-        <v>79</v>
-      </c>
-      <c r="C41" t="s">
-        <v>96</v>
-      </c>
-      <c r="D41" t="s">
-        <v>111</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>19330051920024</v>
-      </c>
-      <c r="B42" t="s">
-        <v>79</v>
-      </c>
-      <c r="C42" t="s">
-        <v>96</v>
-      </c>
-      <c r="D42" t="s">
-        <v>111</v>
-      </c>
-      <c r="E42" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>19330051920032</v>
-      </c>
-      <c r="B43" t="s">
-        <v>80</v>
-      </c>
-      <c r="C43" t="s">
-        <v>97</v>
-      </c>
-      <c r="D43" t="s">
-        <v>112</v>
-      </c>
-      <c r="E43" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>19330051920032</v>
-      </c>
-      <c r="B44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C44" t="s">
-        <v>97</v>
-      </c>
-      <c r="D44" t="s">
-        <v>112</v>
-      </c>
-      <c r="E44" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>19330051920032</v>
-      </c>
-      <c r="B45" t="s">
-        <v>80</v>
-      </c>
-      <c r="C45" t="s">
-        <v>97</v>
-      </c>
-      <c r="D45" t="s">
-        <v>112</v>
-      </c>
-      <c r="E45" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>19330051920032</v>
-      </c>
-      <c r="B46" t="s">
-        <v>80</v>
-      </c>
-      <c r="C46" t="s">
-        <v>97</v>
-      </c>
-      <c r="D46" t="s">
-        <v>112</v>
-      </c>
-      <c r="E46" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>19330051920034</v>
-      </c>
-      <c r="B47" t="s">
-        <v>81</v>
-      </c>
-      <c r="C47" t="s">
-        <v>96</v>
-      </c>
-      <c r="D47" t="s">
-        <v>113</v>
-      </c>
-      <c r="E47" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>19330051920034</v>
-      </c>
-      <c r="B48" t="s">
-        <v>81</v>
-      </c>
-      <c r="C48" t="s">
-        <v>96</v>
-      </c>
-      <c r="D48" t="s">
-        <v>113</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>19330051920034</v>
-      </c>
-      <c r="B49" t="s">
-        <v>81</v>
-      </c>
-      <c r="C49" t="s">
-        <v>96</v>
-      </c>
-      <c r="D49" t="s">
-        <v>113</v>
-      </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>19330051920034</v>
-      </c>
-      <c r="B50" t="s">
-        <v>81</v>
-      </c>
-      <c r="C50" t="s">
-        <v>96</v>
-      </c>
-      <c r="D50" t="s">
-        <v>113</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>19330051920034</v>
-      </c>
-      <c r="B51" t="s">
-        <v>81</v>
-      </c>
-      <c r="C51" t="s">
-        <v>96</v>
-      </c>
-      <c r="D51" t="s">
-        <v>113</v>
-      </c>
-      <c r="E51" t="s">
-        <v>11</v>
-      </c>
-      <c r="F51" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>19330051920038</v>
-      </c>
-      <c r="B52" t="s">
-        <v>82</v>
-      </c>
-      <c r="C52" t="s">
-        <v>98</v>
-      </c>
-      <c r="D52" t="s">
-        <v>114</v>
-      </c>
-      <c r="E52" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>19330051920037</v>
-      </c>
-      <c r="B53" t="s">
-        <v>83</v>
-      </c>
-      <c r="C53" t="s">
-        <v>99</v>
-      </c>
-      <c r="D53" t="s">
-        <v>115</v>
-      </c>
-      <c r="E53" t="s">
-        <v>5</v>
-      </c>
-      <c r="F53" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>19330051920036</v>
-      </c>
-      <c r="B54" t="s">
-        <v>84</v>
-      </c>
-      <c r="C54" t="s">
-        <v>79</v>
-      </c>
-      <c r="D54" t="s">
-        <v>116</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>19330051920036</v>
-      </c>
-      <c r="B55" t="s">
-        <v>84</v>
-      </c>
-      <c r="C55" t="s">
-        <v>79</v>
-      </c>
-      <c r="D55" t="s">
-        <v>116</v>
-      </c>
-      <c r="E55" t="s">
-        <v>5</v>
-      </c>
-      <c r="F55" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>19330051920036</v>
-      </c>
-      <c r="B56" t="s">
-        <v>84</v>
-      </c>
-      <c r="C56" t="s">
-        <v>79</v>
-      </c>
-      <c r="D56" t="s">
-        <v>116</v>
-      </c>
-      <c r="E56" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>19330051920036</v>
-      </c>
-      <c r="B57" t="s">
-        <v>84</v>
-      </c>
-      <c r="C57" t="s">
-        <v>79</v>
-      </c>
-      <c r="D57" t="s">
-        <v>116</v>
-      </c>
-      <c r="E57" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>19330051920036</v>
-      </c>
-      <c r="B58" t="s">
-        <v>84</v>
-      </c>
-      <c r="C58" t="s">
-        <v>79</v>
-      </c>
-      <c r="D58" t="s">
-        <v>116</v>
-      </c>
-      <c r="E58" t="s">
-        <v>9</v>
-      </c>
-      <c r="F58" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>19330051920036</v>
-      </c>
-      <c r="B59" t="s">
-        <v>84</v>
-      </c>
-      <c r="C59" t="s">
-        <v>79</v>
-      </c>
-      <c r="D59" t="s">
-        <v>116</v>
-      </c>
-      <c r="E59" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>19330051920039</v>
-      </c>
-      <c r="B60" t="s">
-        <v>85</v>
-      </c>
-      <c r="C60" t="s">
-        <v>100</v>
-      </c>
-      <c r="D60" t="s">
-        <v>117</v>
-      </c>
-      <c r="E60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>19330051920039</v>
-      </c>
-      <c r="B61" t="s">
-        <v>85</v>
-      </c>
-      <c r="C61" t="s">
-        <v>100</v>
-      </c>
-      <c r="D61" t="s">
-        <v>117</v>
-      </c>
-      <c r="E61" t="s">
-        <v>5</v>
-      </c>
-      <c r="F61" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>19330051920039</v>
-      </c>
-      <c r="B62" t="s">
-        <v>85</v>
-      </c>
-      <c r="C62" t="s">
-        <v>100</v>
-      </c>
-      <c r="D62" t="s">
-        <v>117</v>
-      </c>
-      <c r="E62" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>19330051920039</v>
-      </c>
-      <c r="B63" t="s">
-        <v>85</v>
-      </c>
-      <c r="C63" t="s">
-        <v>100</v>
-      </c>
-      <c r="D63" t="s">
-        <v>117</v>
-      </c>
-      <c r="E63" t="s">
-        <v>9</v>
-      </c>
-      <c r="F63" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>19330051920039</v>
-      </c>
-      <c r="B64" t="s">
-        <v>85</v>
-      </c>
-      <c r="C64" t="s">
-        <v>100</v>
-      </c>
-      <c r="D64" t="s">
-        <v>117</v>
-      </c>
-      <c r="E64" t="s">
-        <v>11</v>
-      </c>
-      <c r="F64" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>19330051920040</v>
-      </c>
-      <c r="B65" t="s">
-        <v>86</v>
-      </c>
-      <c r="C65" t="s">
-        <v>99</v>
-      </c>
-      <c r="D65" t="s">
-        <v>118</v>
-      </c>
-      <c r="E65" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>19330051920040</v>
-      </c>
-      <c r="B66" t="s">
-        <v>86</v>
-      </c>
-      <c r="C66" t="s">
-        <v>99</v>
-      </c>
-      <c r="D66" t="s">
-        <v>118</v>
-      </c>
-      <c r="E66" t="s">
-        <v>5</v>
-      </c>
-      <c r="F66" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>19330051920040</v>
-      </c>
-      <c r="B67" t="s">
-        <v>86</v>
-      </c>
-      <c r="C67" t="s">
-        <v>99</v>
-      </c>
-      <c r="D67" t="s">
-        <v>118</v>
-      </c>
-      <c r="E67" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>19330051920040</v>
-      </c>
-      <c r="B68" t="s">
-        <v>86</v>
-      </c>
-      <c r="C68" t="s">
-        <v>99</v>
-      </c>
-      <c r="D68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E68" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>19330051920040</v>
-      </c>
-      <c r="B69" t="s">
-        <v>86</v>
-      </c>
-      <c r="C69" t="s">
-        <v>99</v>
-      </c>
-      <c r="D69" t="s">
-        <v>118</v>
-      </c>
-      <c r="E69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F69" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>19330051920040</v>
-      </c>
-      <c r="B70" t="s">
-        <v>86</v>
-      </c>
-      <c r="C70" t="s">
-        <v>99</v>
-      </c>
-      <c r="D70" t="s">
-        <v>118</v>
-      </c>
-      <c r="E70" t="s">
-        <v>11</v>
-      </c>
-      <c r="F70" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -6098,87 +5058,87 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920417</v>
+        <v>19330051920014</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920014</v>
+        <v>19330051920422</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920026</v>
+        <v>19330051920036</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920036</v>
+        <v>19330051920039</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920040</v>
+        <v>19330051920417</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6186,84 +5146,84 @@
         <v>19330051920016</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920422</v>
+        <v>19330051920010</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920034</v>
+        <v>19330051920022</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920039</v>
+        <v>19330051920026</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920024</v>
+        <v>18330061460390</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -6271,50 +5231,50 @@
         <v>19330051920032</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920010</v>
+        <v>19330051920038</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
         <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920022</v>
+        <v>19330051920040</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -6322,98 +5282,98 @@
         <v>19330051920003</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>18330051920168</v>
+        <v>19330051920005</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>18330061460390</v>
+        <v>19330051920004</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920038</v>
+        <v>19330051920006</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920037</v>
+        <v>19330051920007</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920005</v>
+        <v>19330051920008</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C20" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D20" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6421,16 +5381,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920004</v>
+        <v>19330051920015</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C21" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D21" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -6438,16 +5398,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920006</v>
+        <v>19330051920012</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -6455,16 +5415,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920007</v>
+        <v>19330051920011</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6472,16 +5432,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920008</v>
+        <v>19330051920009</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D24" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -6489,13 +5449,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920015</v>
+        <v>19330051920017</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D25" t="s">
         <v>145</v>
@@ -6506,13 +5466,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920012</v>
+        <v>19330051920018</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="C26" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D26" t="s">
         <v>146</v>
@@ -6523,13 +5483,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920011</v>
+        <v>18330051920168</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
         <v>147</v>
@@ -6540,13 +5500,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920009</v>
+        <v>19330051920020</v>
       </c>
       <c r="B28" t="s">
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
         <v>148</v>
@@ -6557,13 +5517,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920017</v>
+        <v>19330051920021</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D29" t="s">
         <v>149</v>
@@ -6574,13 +5534,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920018</v>
+        <v>19330051920023</v>
       </c>
       <c r="B30" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C30" t="s">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="D30" t="s">
         <v>150</v>
@@ -6591,13 +5551,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920020</v>
+        <v>19330051920025</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C31" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D31" t="s">
         <v>151</v>
@@ -6608,13 +5568,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920021</v>
+        <v>19330051920027</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="D32" t="s">
         <v>152</v>
@@ -6625,13 +5585,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920023</v>
+        <v>19330051920024</v>
       </c>
       <c r="B33" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="D33" t="s">
         <v>153</v>
@@ -6642,13 +5602,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920025</v>
+        <v>19330051920029</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="C34" t="s">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="D34" t="s">
         <v>154</v>
@@ -6659,13 +5619,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>19330051920027</v>
+        <v>19330051920030</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="C35" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="D35" t="s">
         <v>155</v>
@@ -6676,13 +5636,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>19330051920029</v>
+        <v>19330051920031</v>
       </c>
       <c r="B36" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C36" t="s">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="D36" t="s">
         <v>156</v>
@@ -6693,13 +5653,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>19330051920030</v>
+        <v>19330051920035</v>
       </c>
       <c r="B37" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C37" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D37" t="s">
         <v>157</v>
@@ -6710,13 +5670,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>19330051920031</v>
+        <v>19330051920034</v>
       </c>
       <c r="B38" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C38" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D38" t="s">
         <v>158</v>
@@ -6727,13 +5687,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>19330051920035</v>
+        <v>19330051920037</v>
       </c>
       <c r="B39" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C39" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="D39" t="s">
         <v>159</v>
@@ -6749,7 +5709,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6781,22 +5741,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920003</v>
+        <v>19330051920010</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -6804,68 +5764,68 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>18330051920168</v>
+        <v>19330051920010</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>18330061460390</v>
+        <v>19330051920034</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>61</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920035</v>
+        <v>19330051920034</v>
       </c>
       <c r="B5" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6873,47 +5833,208 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920038</v>
+        <v>19330051920040</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>61</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920037</v>
+        <v>19330051920040</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>60</v>
       </c>
       <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330051920003</v>
+      </c>
+      <c r="B8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>19330051920016</v>
+      </c>
+      <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>18330051920168</v>
+      </c>
+      <c r="B10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" t="s">
+        <v>147</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920022</v>
+      </c>
+      <c r="B11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>18330061460390</v>
+      </c>
+      <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920024</v>
+      </c>
+      <c r="B13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" t="s">
+        <v>135</v>
+      </c>
+      <c r="D13" t="s">
+        <v>153</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330051920038</v>
+      </c>
+      <c r="B14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/5AEM - Estadisticos 20211.xlsx
+++ b/grupos/5AEM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="160">
   <si>
     <t>Materia</t>
   </si>
@@ -254,247 +254,247 @@
     <t>SERRANO</t>
   </si>
   <si>
+    <t>VALDERRAMA</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MENCIAS</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>FERNANDO DE JESUS</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>ESTEFANY SARAI</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>NATANAEL</t>
+  </si>
+  <si>
+    <t>YAMIL ELIEL</t>
+  </si>
+  <si>
+    <t>EMILIO</t>
+  </si>
+  <si>
+    <t>ALAN EDUARDO</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BALDEZ</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>VALDERRAMA</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>MORAN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>IXTACUA</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>PALAGOT</t>
+  </si>
+  <si>
+    <t>BELTRAN</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>YEPEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>MELLADO</t>
   </si>
   <si>
     <t>CHICO</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MENCIAS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>FERNANDO DE JESUS</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>ESTEFANY SARAI</t>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>CARLOS ALBERTO</t>
+  </si>
+  <si>
+    <t>ALEX SAUL</t>
+  </si>
+  <si>
+    <t>CRISTIAN ANTONIO</t>
+  </si>
+  <si>
+    <t>ALBERTO</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>HAZIEL</t>
+  </si>
+  <si>
+    <t>GIOVANNA</t>
+  </si>
+  <si>
+    <t>SAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>LOGAN ZURIEL</t>
+  </si>
+  <si>
+    <t>YAIR ANTONIO</t>
+  </si>
+  <si>
+    <t>HUGO</t>
   </si>
   <si>
     <t>RAFAEL</t>
   </si>
   <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>NATANAEL</t>
-  </si>
-  <si>
-    <t>YAMIL ELIEL</t>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>JOSE AUGUSTO</t>
+  </si>
+  <si>
+    <t>DIANA AMEYALLI</t>
+  </si>
+  <si>
+    <t>ANUAR ANTONIO</t>
+  </si>
+  <si>
+    <t>ELIDETH</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>ARLETH</t>
+  </si>
+  <si>
+    <t>JAHIR</t>
+  </si>
+  <si>
+    <t>JOCELYN BERENICE</t>
+  </si>
+  <si>
+    <t>JOHNNY</t>
   </si>
   <si>
     <t>ERICK ORLANDO</t>
-  </si>
-  <si>
-    <t>EMILIO</t>
-  </si>
-  <si>
-    <t>ALAN EDUARDO</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BALDEZ</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>MORAN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>IXTACUA</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>PALAGOT</t>
-  </si>
-  <si>
-    <t>BELTRAN</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>YEPEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>MELLADO</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>CARLOS ALBERTO</t>
-  </si>
-  <si>
-    <t>ALEX SAUL</t>
-  </si>
-  <si>
-    <t>CRISTIAN ANTONIO</t>
-  </si>
-  <si>
-    <t>ALBERTO</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>HAZIEL</t>
-  </si>
-  <si>
-    <t>GIOVANNA</t>
-  </si>
-  <si>
-    <t>SAUL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>LOGAN ZURIEL</t>
-  </si>
-  <si>
-    <t>YAIR ANTONIO</t>
-  </si>
-  <si>
-    <t>HUGO</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>JOSE AUGUSTO</t>
-  </si>
-  <si>
-    <t>DIANA AMEYALLI</t>
-  </si>
-  <si>
-    <t>ANUAR ANTONIO</t>
-  </si>
-  <si>
-    <t>ELIDETH</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>ARLETH</t>
-  </si>
-  <si>
-    <t>JAHIR</t>
-  </si>
-  <si>
-    <t>JOCELYN BERENICE</t>
-  </si>
-  <si>
-    <t>JOHNNY</t>
   </si>
   <si>
     <t>MAURICIO</t>
@@ -1035,7 +1035,7 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>10</v>
@@ -1077,7 +1077,7 @@
         <v>10</v>
       </c>
       <c r="AB4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC4">
         <v>10</v>
@@ -1124,7 +1124,7 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>10</v>
@@ -1213,7 +1213,7 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>10</v>
@@ -1302,7 +1302,7 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>10</v>
@@ -1569,7 +1569,7 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>10</v>
@@ -1658,7 +1658,7 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>10</v>
@@ -1700,7 +1700,7 @@
         <v>10</v>
       </c>
       <c r="AB11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC11">
         <v>10</v>
@@ -1747,7 +1747,7 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>10</v>
@@ -1789,7 +1789,7 @@
         <v>10</v>
       </c>
       <c r="AB12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC12">
         <v>10</v>
@@ -1836,7 +1836,7 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>10</v>
@@ -2103,7 +2103,7 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>10</v>
@@ -2281,7 +2281,7 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>10</v>
@@ -2370,7 +2370,7 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>10</v>
@@ -2459,7 +2459,7 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
         <v>6</v>
@@ -2637,7 +2637,7 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>10</v>
@@ -2705,7 +2705,7 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H23">
         <v>10</v>
@@ -2726,7 +2726,7 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>10</v>
@@ -2768,7 +2768,7 @@
         <v>10</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC23">
         <v>10</v>
@@ -2815,7 +2815,7 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>10</v>
@@ -2904,7 +2904,7 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>10</v>
@@ -3260,7 +3260,7 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>10</v>
@@ -3349,7 +3349,7 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>10</v>
@@ -3438,7 +3438,7 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>10</v>
@@ -3480,7 +3480,7 @@
         <v>10</v>
       </c>
       <c r="AB31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC31">
         <v>10</v>
@@ -3527,7 +3527,7 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
         <v>10</v>
@@ -3616,7 +3616,7 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>10</v>
@@ -3794,7 +3794,7 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O35">
         <v>10</v>
@@ -3883,7 +3883,7 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>10</v>
@@ -4129,7 +4129,7 @@
         <v>10</v>
       </c>
       <c r="G39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H39">
         <v>10</v>
@@ -4150,7 +4150,7 @@
         <v>10</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
         <v>10</v>
@@ -4192,7 +4192,7 @@
         <v>10</v>
       </c>
       <c r="AB39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC39">
         <v>10</v>
@@ -4438,25 +4438,25 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>68.42</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>31.58</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4658,7 +4658,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4693,10 +4693,10 @@
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -4713,10 +4713,10 @@
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4733,10 +4733,10 @@
         <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4753,10 +4753,10 @@
         <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4773,10 +4773,10 @@
         <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -4793,10 +4793,10 @@
         <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4813,10 +4813,10 @@
         <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -4827,16 +4827,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920022</v>
+        <v>19330051920026</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -4847,16 +4847,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920026</v>
+        <v>18330061460390</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -4867,16 +4867,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>18330061460390</v>
+        <v>19330051920032</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -4887,16 +4887,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920032</v>
+        <v>19330051920036</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -4907,36 +4907,36 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920038</v>
+        <v>19330051920036</v>
       </c>
       <c r="B13" t="s">
         <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920036</v>
+        <v>19330051920039</v>
       </c>
       <c r="B14" t="s">
         <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -4947,16 +4947,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920036</v>
+        <v>19330051920039</v>
       </c>
       <c r="B15" t="s">
         <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
@@ -4967,61 +4967,21 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920039</v>
+        <v>19330051920040</v>
       </c>
       <c r="B16" t="s">
         <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>19330051920039</v>
-      </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" t="s">
-        <v>106</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>19330051920040</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" t="s">
-        <v>107</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
         <v>60</v>
       </c>
     </row>
@@ -5064,10 +5024,10 @@
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -5081,10 +5041,10 @@
         <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -5095,13 +5055,13 @@
         <v>19330051920036</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -5112,13 +5072,13 @@
         <v>19330051920039</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -5132,10 +5092,10 @@
         <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -5149,10 +5109,10 @@
         <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -5166,10 +5126,10 @@
         <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -5177,16 +5137,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920022</v>
+        <v>19330051920026</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5194,16 +5154,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920026</v>
+        <v>18330061460390</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -5211,16 +5171,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>18330061460390</v>
+        <v>19330051920032</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -5228,16 +5188,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920032</v>
+        <v>19330051920040</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -5245,47 +5205,47 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920038</v>
+        <v>19330051920003</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920040</v>
+        <v>19330051920005</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920003</v>
+        <v>19330051920004</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
         <v>137</v>
@@ -5296,16 +5256,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920005</v>
+        <v>19330051920006</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C16" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D16" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -5313,16 +5273,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920004</v>
+        <v>19330051920007</v>
       </c>
       <c r="B17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -5330,16 +5290,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920006</v>
+        <v>19330051920008</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -5347,16 +5307,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920007</v>
+        <v>19330051920015</v>
       </c>
       <c r="B19" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -5364,16 +5324,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920008</v>
+        <v>19330051920012</v>
       </c>
       <c r="B20" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D20" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5381,13 +5341,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920015</v>
+        <v>19330051920011</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D21" t="s">
         <v>141</v>
@@ -5398,13 +5358,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920012</v>
+        <v>19330051920009</v>
       </c>
       <c r="B22" t="s">
         <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
         <v>142</v>
@@ -5415,13 +5375,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920011</v>
+        <v>19330051920017</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D23" t="s">
         <v>143</v>
@@ -5432,13 +5392,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920009</v>
+        <v>19330051920018</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D24" t="s">
         <v>144</v>
@@ -5449,13 +5409,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920017</v>
+        <v>18330051920168</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
         <v>145</v>
@@ -5466,13 +5426,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920018</v>
+        <v>19330051920020</v>
       </c>
       <c r="B26" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s">
         <v>146</v>
@@ -5483,13 +5443,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>18330051920168</v>
+        <v>19330051920022</v>
       </c>
       <c r="B27" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="D27" t="s">
         <v>147</v>
@@ -5500,13 +5460,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920020</v>
+        <v>19330051920021</v>
       </c>
       <c r="B28" t="s">
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="D28" t="s">
         <v>148</v>
@@ -5517,13 +5477,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920021</v>
+        <v>19330051920023</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="C29" t="s">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="D29" t="s">
         <v>149</v>
@@ -5534,13 +5494,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920023</v>
+        <v>19330051920025</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="D30" t="s">
         <v>150</v>
@@ -5551,13 +5511,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920025</v>
+        <v>19330051920027</v>
       </c>
       <c r="B31" t="s">
         <v>75</v>
       </c>
       <c r="C31" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s">
         <v>151</v>
@@ -5568,13 +5528,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920027</v>
+        <v>19330051920024</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D32" t="s">
         <v>152</v>
@@ -5585,13 +5545,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920024</v>
+        <v>19330051920029</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="C33" t="s">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="D33" t="s">
         <v>153</v>
@@ -5602,13 +5562,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920029</v>
+        <v>19330051920030</v>
       </c>
       <c r="B34" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C34" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="D34" t="s">
         <v>154</v>
@@ -5619,13 +5579,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>19330051920030</v>
+        <v>19330051920031</v>
       </c>
       <c r="B35" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C35" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D35" t="s">
         <v>155</v>
@@ -5636,13 +5596,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>19330051920031</v>
+        <v>19330051920035</v>
       </c>
       <c r="B36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C36" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="D36" t="s">
         <v>156</v>
@@ -5653,13 +5613,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>19330051920035</v>
+        <v>19330051920034</v>
       </c>
       <c r="B37" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C37" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="D37" t="s">
         <v>157</v>
@@ -5670,13 +5630,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>19330051920034</v>
+        <v>19330051920038</v>
       </c>
       <c r="B38" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D38" t="s">
         <v>158</v>
@@ -5690,10 +5650,10 @@
         <v>19330051920037</v>
       </c>
       <c r="B39" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C39" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D39" t="s">
         <v>159</v>
@@ -5709,7 +5669,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5747,10 +5707,10 @@
         <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5770,10 +5730,10 @@
         <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -5790,13 +5750,13 @@
         <v>19330051920034</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5813,13 +5773,13 @@
         <v>19330051920034</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -5836,13 +5796,13 @@
         <v>19330051920040</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5859,13 +5819,13 @@
         <v>19330051920040</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5882,13 +5842,13 @@
         <v>19330051920003</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5908,10 +5868,10 @@
         <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -5928,13 +5888,13 @@
         <v>18330051920168</v>
       </c>
       <c r="B10" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C10" t="s">
         <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5948,16 +5908,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920022</v>
+        <v>18330061460390</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
         <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -5971,71 +5931,25 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>18330061460390</v>
+        <v>19330051920024</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920024</v>
-      </c>
-      <c r="B13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C13" t="s">
-        <v>135</v>
-      </c>
-      <c r="D13" t="s">
-        <v>153</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920038</v>
-      </c>
-      <c r="B14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" t="s">
-        <v>104</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5AEM - Estadisticos 20211.xlsx
+++ b/grupos/5AEM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="160">
   <si>
     <t>Materia</t>
   </si>
@@ -200,21 +200,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
+    <t>Cruz Alejo José Armando</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
-    <t>Cruz Alejo José Armando</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
     <t>Aurioles Maldonado Luis Gustavo</t>
   </si>
   <si>
@@ -230,30 +230,84 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BALDEZ</t>
+  </si>
+  <si>
     <t>BONILLA</t>
   </si>
   <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>ENCARNACION</t>
   </si>
   <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>RIOS</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
     <t>ROMAN</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>SERRANO</t>
   </si>
   <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
     <t>VALDERRAMA</t>
   </si>
   <si>
@@ -263,19 +317,55 @@
     <t>VILLEGAS</t>
   </si>
   <si>
+    <t>MORAN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>IXTACUA</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>PALAGOT</t>
+  </si>
+  <si>
     <t>BERISTAIN</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
+    <t>BELTRAN</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>SORIANO</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>YEPEZ</t>
   </si>
   <si>
     <t>CHAVEZ</t>
@@ -284,220 +374,130 @@
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
+    <t>MELLADO</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>MENCIAS</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>CARLOS ALBERTO</t>
+  </si>
+  <si>
+    <t>ALEX SAUL</t>
   </si>
   <si>
     <t>FERNANDO DE JESUS</t>
   </si>
   <si>
+    <t>CRISTIAN ANTONIO</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
     <t>LUIS ENRIQUE</t>
   </si>
   <si>
     <t>JESSICA</t>
   </si>
   <si>
+    <t>ALBERTO</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>HAZIEL</t>
+  </si>
+  <si>
+    <t>GIOVANNA</t>
+  </si>
+  <si>
     <t>JESUS</t>
   </si>
   <si>
+    <t>SAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>LOGAN ZURIEL</t>
+  </si>
+  <si>
+    <t>YAIR ANTONIO</t>
+  </si>
+  <si>
     <t>ESTEFANY SARAI</t>
   </si>
   <si>
+    <t>HUGO</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>JOSE AUGUSTO</t>
+  </si>
+  <si>
     <t>ISRAEL</t>
   </si>
   <si>
     <t>NATANAEL</t>
   </si>
   <si>
+    <t>DIANA AMEYALLI</t>
+  </si>
+  <si>
+    <t>ANUAR ANTONIO</t>
+  </si>
+  <si>
+    <t>ELIDETH</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>ARLETH</t>
+  </si>
+  <si>
     <t>YAMIL ELIEL</t>
   </si>
   <si>
+    <t>JAHIR</t>
+  </si>
+  <si>
+    <t>JOCELYN BERENICE</t>
+  </si>
+  <si>
+    <t>JOHNNY</t>
+  </si>
+  <si>
+    <t>ERICK ORLANDO</t>
+  </si>
+  <si>
+    <t>MAURICIO</t>
+  </si>
+  <si>
     <t>EMILIO</t>
   </si>
   <si>
     <t>ALAN EDUARDO</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BALDEZ</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>MORAN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>IXTACUA</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>PALAGOT</t>
-  </si>
-  <si>
-    <t>BELTRAN</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>YEPEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>MELLADO</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>CARLOS ALBERTO</t>
-  </si>
-  <si>
-    <t>ALEX SAUL</t>
-  </si>
-  <si>
-    <t>CRISTIAN ANTONIO</t>
-  </si>
-  <si>
-    <t>ALBERTO</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>HAZIEL</t>
-  </si>
-  <si>
-    <t>GIOVANNA</t>
-  </si>
-  <si>
-    <t>SAUL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>LOGAN ZURIEL</t>
-  </si>
-  <si>
-    <t>YAIR ANTONIO</t>
-  </si>
-  <si>
-    <t>HUGO</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>JOSE AUGUSTO</t>
-  </si>
-  <si>
-    <t>DIANA AMEYALLI</t>
-  </si>
-  <si>
-    <t>ANUAR ANTONIO</t>
-  </si>
-  <si>
-    <t>ELIDETH</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>ARLETH</t>
-  </si>
-  <si>
-    <t>JAHIR</t>
-  </si>
-  <si>
-    <t>JOCELYN BERENICE</t>
-  </si>
-  <si>
-    <t>JOHNNY</t>
-  </si>
-  <si>
-    <t>ERICK ORLANDO</t>
-  </si>
-  <si>
-    <t>MAURICIO</t>
   </si>
 </sst>
 </file>
@@ -1041,43 +1041,43 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>8</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA4">
         <v>10</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC4">
         <v>10</v>
@@ -1130,25 +1130,25 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>9</v>
@@ -1219,25 +1219,25 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1308,25 +1308,25 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -1370,7 +1370,7 @@
         <v>6</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H8">
         <v>6</v>
@@ -1391,31 +1391,31 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>6</v>
@@ -1427,13 +1427,13 @@
         <v>6</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA8">
         <v>6</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC8">
         <v>6</v>
@@ -1480,37 +1480,37 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
         <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1575,25 +1575,25 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>10</v>
@@ -1605,7 +1605,7 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA10">
         <v>10</v>
@@ -1664,25 +1664,25 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1694,13 +1694,13 @@
         <v>8</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA11">
         <v>10</v>
       </c>
       <c r="AB11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC11">
         <v>10</v>
@@ -1753,25 +1753,25 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>7</v>
@@ -1780,7 +1780,7 @@
         <v>9</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z12">
         <v>7</v>
@@ -1842,25 +1842,25 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1889,7 +1889,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -1910,7 +1910,7 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>6</v>
@@ -1925,49 +1925,49 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>7</v>
       </c>
       <c r="Z14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA14">
         <v>10</v>
       </c>
       <c r="AB14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC14">
         <v>10</v>
@@ -1978,7 +1978,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>7</v>
@@ -1993,13 +1993,13 @@
         <v>6</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H15">
         <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
         <v>9</v>
@@ -2014,40 +2014,40 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X15">
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z15">
         <v>5</v>
@@ -2056,7 +2056,7 @@
         <v>6</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC15">
         <v>6</v>
@@ -2109,37 +2109,37 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>10</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>9</v>
       </c>
       <c r="Z16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA16">
         <v>10</v>
@@ -2171,7 +2171,7 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H17">
         <v>10</v>
@@ -2192,31 +2192,31 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -2234,7 +2234,7 @@
         <v>10</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC17">
         <v>10</v>
@@ -2287,25 +2287,25 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>10</v>
@@ -2317,7 +2317,7 @@
         <v>9</v>
       </c>
       <c r="Z18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA18">
         <v>10</v>
@@ -2376,34 +2376,34 @@
         <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>10</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z19">
         <v>9</v>
@@ -2465,43 +2465,43 @@
         <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>7</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA20">
         <v>7</v>
       </c>
       <c r="AB20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC20">
         <v>7</v>
@@ -2512,7 +2512,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C21">
         <v>6</v>
@@ -2527,13 +2527,13 @@
         <v>6</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H21">
         <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>5</v>
@@ -2548,37 +2548,37 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>5</v>
@@ -2590,7 +2590,7 @@
         <v>6</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>6</v>
@@ -2643,25 +2643,25 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -2673,7 +2673,7 @@
         <v>8</v>
       </c>
       <c r="Z22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -2732,31 +2732,31 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>9</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2768,7 +2768,7 @@
         <v>10</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC23">
         <v>10</v>
@@ -2821,34 +2821,34 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>10</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z24">
         <v>8</v>
@@ -2910,25 +2910,25 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2940,7 +2940,7 @@
         <v>8</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA25">
         <v>10</v>
@@ -2993,43 +2993,43 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>7</v>
       </c>
       <c r="Z26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA26">
         <v>6</v>
@@ -3061,7 +3061,7 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H27">
         <v>10</v>
@@ -3082,34 +3082,34 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
         <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>8</v>
@@ -3118,13 +3118,13 @@
         <v>8</v>
       </c>
       <c r="Z27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA27">
         <v>10</v>
       </c>
       <c r="AB27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC27">
         <v>10</v>
@@ -3150,7 +3150,7 @@
         <v>6</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H28">
         <v>6</v>
@@ -3171,31 +3171,31 @@
         <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>6</v>
@@ -3204,16 +3204,16 @@
         <v>5</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC28">
         <v>6</v>
@@ -3266,25 +3266,25 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>10</v>
@@ -3355,25 +3355,25 @@
         <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W30">
         <v>10</v>
@@ -3444,37 +3444,37 @@
         <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W31">
         <v>8</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>7</v>
       </c>
       <c r="Z31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA31">
         <v>10</v>
@@ -3533,25 +3533,25 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>10</v>
@@ -3622,25 +3622,25 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3684,13 +3684,13 @@
         <v>10</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H34">
         <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J34">
         <v>6</v>
@@ -3705,49 +3705,49 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O34">
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA34">
         <v>10</v>
       </c>
       <c r="AB34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC34">
         <v>10</v>
@@ -3800,37 +3800,37 @@
         <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W35">
         <v>7</v>
       </c>
       <c r="X35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA35">
         <v>9</v>
@@ -3889,25 +3889,25 @@
         <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W36">
         <v>10</v>
@@ -3936,7 +3936,7 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C37">
         <v>5</v>
@@ -3951,13 +3951,13 @@
         <v>6</v>
       </c>
       <c r="G37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H37">
         <v>6</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J37">
         <v>6</v>
@@ -3972,49 +3972,49 @@
         <v>6</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA37">
         <v>6</v>
       </c>
       <c r="AB37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC37">
         <v>6</v>
@@ -4061,31 +4061,31 @@
         <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O38">
         <v>10</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W38">
         <v>8</v>
@@ -4094,16 +4094,16 @@
         <v>6</v>
       </c>
       <c r="Y38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA38">
         <v>10</v>
       </c>
       <c r="AB38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC38">
         <v>10</v>
@@ -4156,25 +4156,25 @@
         <v>10</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W39">
         <v>10</v>
@@ -4183,7 +4183,7 @@
         <v>8</v>
       </c>
       <c r="Y39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z39">
         <v>8</v>
@@ -4203,7 +4203,7 @@
         <v>49</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C40">
         <v>6</v>
@@ -4218,13 +4218,13 @@
         <v>6</v>
       </c>
       <c r="G40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H40">
         <v>10</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J40">
         <v>6</v>
@@ -4239,34 +4239,34 @@
         <v>6</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O40">
         <v>8</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X40">
         <v>6</v>
@@ -4275,16 +4275,16 @@
         <v>5</v>
       </c>
       <c r="Z40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA40">
         <v>6</v>
       </c>
       <c r="AB40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC40">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -4307,7 +4307,7 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H41">
         <v>10</v>
@@ -4328,52 +4328,52 @@
         <v>10</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O41">
         <v>10</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W41">
         <v>7</v>
       </c>
       <c r="X41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y41">
         <v>6</v>
       </c>
       <c r="Z41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC41">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -4429,7 +4429,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
@@ -4438,25 +4438,25 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>73.68000000000001</v>
+        <v>86.84</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>13.16</v>
       </c>
       <c r="H2">
-        <v>9.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4470,19 +4470,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>73.68000000000001</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="G3">
-        <v>26.32</v>
+        <v>5.26</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4502,19 +4502,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>78.95</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="G4">
-        <v>21.05</v>
+        <v>5.26</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4534,16 +4534,16 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>81.58</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="G5">
-        <v>18.42</v>
+        <v>5.26</v>
       </c>
       <c r="H5">
         <v>7.7</v>
@@ -4557,7 +4557,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
@@ -4566,25 +4566,25 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>86.84</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>13.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4642,7 +4642,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4658,7 +4658,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4683,306 +4683,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920417</v>
-      </c>
-      <c r="B2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920014</v>
-      </c>
-      <c r="B3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920014</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920016</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920010</v>
-      </c>
-      <c r="B6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920422</v>
-      </c>
-      <c r="B7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920422</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" t="s">
-        <v>96</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920026</v>
-      </c>
-      <c r="B9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>18330061460390</v>
-      </c>
-      <c r="B10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920032</v>
-      </c>
-      <c r="B11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" t="s">
-        <v>99</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920036</v>
-      </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920036</v>
-      </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920039</v>
-      </c>
-      <c r="B14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" t="s">
-        <v>101</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920039</v>
-      </c>
-      <c r="B15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920040</v>
-      </c>
-      <c r="B16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" t="s">
-        <v>102</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -5018,70 +4718,70 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920014</v>
+        <v>19330051920003</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920422</v>
+        <v>19330051920005</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920036</v>
+        <v>19330051920004</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920039</v>
+        <v>19330051920006</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5089,132 +4789,132 @@
         <v>19330051920417</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920016</v>
+        <v>19330051920007</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920010</v>
+        <v>19330051920008</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920026</v>
+        <v>19330051920014</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>18330061460390</v>
+        <v>19330051920016</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920032</v>
+        <v>19330051920015</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920040</v>
+        <v>19330051920012</v>
       </c>
       <c r="B12" t="s">
         <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920003</v>
+        <v>19330051920011</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -5222,16 +4922,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920005</v>
+        <v>19330051920009</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -5239,16 +4939,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920004</v>
+        <v>19330051920010</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -5256,16 +4956,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920006</v>
+        <v>19330051920017</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -5273,13 +4973,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920007</v>
+        <v>19330051920018</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
         <v>138</v>
@@ -5290,16 +4990,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920008</v>
+        <v>18330051920168</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -5307,16 +5007,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920015</v>
+        <v>19330051920422</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -5324,16 +5024,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920012</v>
+        <v>19330051920020</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5341,16 +5041,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920011</v>
+        <v>19330051920022</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -5358,16 +5058,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920009</v>
+        <v>19330051920021</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -5375,16 +5075,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920017</v>
+        <v>19330051920023</v>
       </c>
       <c r="B23" t="s">
         <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -5392,16 +5092,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920018</v>
+        <v>19330051920026</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="D24" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -5409,16 +5109,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>18330051920168</v>
+        <v>18330061460390</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -5426,16 +5126,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920020</v>
+        <v>19330051920025</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -5443,16 +5143,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920022</v>
+        <v>19330051920027</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="D27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -5460,16 +5160,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920021</v>
+        <v>19330051920024</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -5477,16 +5177,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920023</v>
+        <v>19330051920029</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D29" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -5494,16 +5194,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920025</v>
+        <v>19330051920030</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -5511,16 +5211,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920027</v>
+        <v>19330051920032</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -5528,16 +5228,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920024</v>
+        <v>19330051920031</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -5545,16 +5245,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920029</v>
+        <v>19330051920035</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="D33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -5562,16 +5262,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920030</v>
+        <v>19330051920034</v>
       </c>
       <c r="B34" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D34" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -5579,16 +5279,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>19330051920031</v>
+        <v>19330051920038</v>
       </c>
       <c r="B35" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -5596,16 +5296,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>19330051920035</v>
+        <v>19330051920037</v>
       </c>
       <c r="B36" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C36" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D36" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -5613,16 +5313,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>19330051920034</v>
+        <v>19330051920036</v>
       </c>
       <c r="B37" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="C37" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="D37" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -5630,16 +5330,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>19330051920038</v>
+        <v>19330051920039</v>
       </c>
       <c r="B38" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="D38" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -5647,16 +5347,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>19330051920037</v>
+        <v>19330051920040</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C39" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="D39" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -5669,7 +5369,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5701,45 +5401,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920010</v>
+        <v>19330051920014</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920010</v>
+        <v>19330051920014</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5747,22 +5447,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920034</v>
+        <v>19330051920039</v>
       </c>
       <c r="B4" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5770,16 +5470,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920034</v>
+        <v>19330051920039</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -5793,16 +5493,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920040</v>
+        <v>19330051920417</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5816,45 +5516,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920040</v>
+        <v>19330051920026</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920003</v>
+        <v>19330051920032</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
         <v>119</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5862,93 +5562,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920016</v>
+        <v>19330051920036</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>158</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>60</v>
       </c>
       <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>18330051920168</v>
-      </c>
-      <c r="B10" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" t="s">
-        <v>145</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>18330061460390</v>
-      </c>
-      <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920024</v>
-      </c>
-      <c r="B12" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" t="s">
-        <v>132</v>
-      </c>
-      <c r="D12" t="s">
-        <v>152</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>
